--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488022_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488022_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>14.5784</v>
+        <v>13.5118</v>
       </c>
       <c r="E2" t="n">
-        <v>12.2785</v>
+        <v>11.5489</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2998</v>
+        <v>1.9629</v>
       </c>
       <c r="G2" t="n">
         <v>7.3262</v>
@@ -610,13 +610,13 @@
         <v>3.1716</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8735</v>
+        <v>1.8069</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6579</v>
+        <v>1.9283</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2156</v>
+        <v>-0.1213</v>
       </c>
       <c r="V2" t="n">
         <v>1.2071</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. VALEIRAS CREUS</t>
+          <t>L. SIGISMONTI RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4013</v>
+        <v>5.9898</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4387</v>
+        <v>6.6052</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9626</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9924</v>
+        <v>3.8224</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4931</v>
+        <v>3.3573</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4992</v>
+        <v>0.465</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8437</v>
+        <v>6.4227</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9598</v>
+        <v>5.1655</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8839</v>
+        <v>1.2572</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8513</v>
+        <v>-2.6003</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.4666</v>
+        <v>-1.8081</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3847</v>
+        <v>-0.7922</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9911</v>
+        <v>1.784</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.9733</v>
+        <v>1.784</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2107</v>
+        <v>0.7204</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1036</v>
+        <v>0.5195</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1071</v>
+        <v>0.2009</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2071</v>
+        <v>-0.337</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4737</v>
+        <v>-0.337</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. SIGISMONTI RODRIGUEZ</t>
+          <t>J. VALEIRAS CREUS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.8703</v>
+        <v>5.7443</v>
       </c>
       <c r="E4" t="n">
-        <v>6.4015</v>
+        <v>4.7256</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5312</v>
+        <v>1.0187</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8224</v>
+        <v>1.9924</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3573</v>
+        <v>1.4931</v>
       </c>
       <c r="I4" t="n">
-        <v>0.465</v>
+        <v>0.4992</v>
       </c>
       <c r="J4" t="n">
-        <v>6.4227</v>
+        <v>3.8437</v>
       </c>
       <c r="K4" t="n">
-        <v>5.1655</v>
+        <v>2.9598</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2572</v>
+        <v>0.8839</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.6003</v>
+        <v>-1.8513</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.8081</v>
+        <v>-1.4666</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7922</v>
+        <v>-0.3847</v>
       </c>
       <c r="P4" t="n">
-        <v>1.784</v>
+        <v>0.9911</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R4" t="n">
-        <v>1.784</v>
+        <v>2.9733</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6009</v>
+        <v>1.5537</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3158</v>
+        <v>1.3905</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2851</v>
+        <v>0.1632</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.337</v>
+        <v>1.2071</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.337</v>
+        <v>1.4737</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. AVALOS ORTIZ</t>
+          <t>S. MELERO ZURITA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.648</v>
+        <v>4.7793</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2506</v>
+        <v>3.503</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3974</v>
+        <v>1.2763</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7772</v>
+        <v>2.8931</v>
       </c>
       <c r="H5" t="n">
-        <v>2.131</v>
+        <v>1.5516</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3538</v>
+        <v>1.3414</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6285</v>
+        <v>2.579</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7334</v>
+        <v>0.9887</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.105</v>
+        <v>1.5903</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8513</v>
+        <v>0.3141</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6024</v>
+        <v>0.5629</v>
       </c>
       <c r="O5" t="n">
         <v>-0.2488</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1893</v>
+        <v>1.9822</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1805</v>
+        <v>2.9733</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2078</v>
+        <v>1.0407</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1396</v>
+        <v>1.3115</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0682</v>
+        <v>-0.2709</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4737</v>
+        <v>-1.1367</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4737</v>
+        <v>0.6036</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. MELERO ZURITA</t>
+          <t>P. AVALOS ORTIZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1626</v>
+        <v>4.7146</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1952</v>
+        <v>4.1488</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9674</v>
+        <v>0.5658</v>
       </c>
       <c r="G6" t="n">
-        <v>2.8931</v>
+        <v>1.7772</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5516</v>
+        <v>2.131</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3414</v>
+        <v>-0.3538</v>
       </c>
       <c r="J6" t="n">
-        <v>2.579</v>
+        <v>3.6285</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9887</v>
+        <v>3.7334</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5903</v>
+        <v>-0.105</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3141</v>
+        <v>-1.8513</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5629</v>
+        <v>-1.6024</v>
       </c>
       <c r="O6" t="n">
         <v>-0.2488</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9822</v>
+        <v>1.1893</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>2.9733</v>
+        <v>2.1805</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.576</v>
+        <v>0.2744</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0038</v>
+        <v>0.0377</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5797</v>
+        <v>0.2367</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1367</v>
+        <v>1.4737</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6036</v>
+        <v>1.4737</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.7403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. JUZBASIC</t>
+          <t>R. REVELLES DIAZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2076</v>
+        <v>1.6884</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7197</v>
+        <v>0.6923</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4879</v>
+        <v>0.996</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2978</v>
+        <v>-1.4037</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3927</v>
+        <v>-1.8666</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6905</v>
+        <v>0.4629</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6783</v>
+        <v>-0.09959999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3859</v>
+        <v>-0.9472</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7076</v>
+        <v>0.8476</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9761</v>
+        <v>-1.3041</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9932</v>
+        <v>-0.9194</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0171</v>
+        <v>-0.3847</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9822</v>
+        <v>2.5769</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9019</v>
+        <v>0.2991</v>
       </c>
       <c r="T8" t="n">
-        <v>0.213</v>
+        <v>0.3094</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6888</v>
+        <v>-0.0103</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6036</v>
+        <v>1.2071</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8107</v>
+        <v>1.4737</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2071</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0012</v>
+        <v>1.1135</v>
       </c>
       <c r="E9" t="n">
         <v>1.2363</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2351</v>
+        <v>-0.1228</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7549</v>
@@ -1156,13 +1156,13 @@
         <v>1.5858</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1615</v>
+        <v>1.2738</v>
       </c>
       <c r="T9" t="n">
         <v>1.0573</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1042</v>
+        <v>0.2165</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. REVELLES DIAZ</t>
+          <t>D. JUZBASIC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8162</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2079</v>
+        <v>0.8051</v>
       </c>
       <c r="F10" t="n">
-        <v>1.0241</v>
+        <v>0.1228</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4037</v>
+        <v>-0.2978</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8666</v>
+        <v>0.3927</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4629</v>
+        <v>-0.6905</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.09959999999999999</v>
+        <v>0.6783</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9472</v>
+        <v>1.3859</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8476</v>
+        <v>-0.7076</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3041</v>
+        <v>-0.9761</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9194</v>
+        <v>-0.9932</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3847</v>
+        <v>0.0171</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5769</v>
+        <v>1.9822</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5731000000000001</v>
+        <v>0.6222</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5909</v>
+        <v>0.2984</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0178</v>
+        <v>0.3238</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2071</v>
+        <v>0.6036</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4737</v>
+        <v>1.8107</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2666</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="11">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.4526</v>
+        <v>-0.6168</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0942</v>
+        <v>-2.3145</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6416</v>
+        <v>1.6977</v>
       </c>
       <c r="G13" t="n">
         <v>-1.4409</v>
@@ -1468,13 +1468,13 @@
         <v>2.3787</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5918</v>
+        <v>0.4276</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7564</v>
+        <v>0.5361</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1646</v>
+        <v>-0.1084</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.8961</v>
+        <v>-0.738</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.4679</v>
+        <v>-1.3661</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5719</v>
+        <v>0.628</v>
       </c>
       <c r="G14" t="n">
         <v>-0.4072</v>
@@ -1546,13 +1546,13 @@
         <v>0.5947</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.359</v>
+        <v>-0.201</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1248</v>
+        <v>-0.0229</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2342</v>
+        <v>-0.1781</v>
       </c>
       <c r="V14" t="n">
         <v>0.2666</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.1538</v>
+        <v>-1.9957</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.7256</v>
+        <v>-2.6238</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5719</v>
+        <v>0.628</v>
       </c>
       <c r="G15" t="n">
         <v>-0.4072</v>
@@ -1624,13 +1624,13 @@
         <v>0.5947</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.359</v>
+        <v>-0.201</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1248</v>
+        <v>-0.0229</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2342</v>
+        <v>-0.1781</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>37.19910000000001</v>
+        <v>38.1351</v>
       </c>
       <c r="E16" t="n">
-        <v>29.04089999999999</v>
+        <v>29.97679999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>8.158300000000001</v>
+        <v>8.157999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>16.1156</v>
@@ -1675,19 +1675,19 @@
         <v>0.5934999999999997</v>
       </c>
       <c r="J16" t="n">
-        <v>27.54669999999999</v>
+        <v>27.5467</v>
       </c>
       <c r="K16" t="n">
         <v>21.7479</v>
       </c>
       <c r="L16" t="n">
-        <v>5.7988</v>
+        <v>5.798799999999998</v>
       </c>
       <c r="M16" t="n">
         <v>-11.4311</v>
       </c>
       <c r="N16" t="n">
-        <v>-6.225899999999998</v>
+        <v>-6.225899999999999</v>
       </c>
       <c r="O16" t="n">
         <v>-5.2052</v>
@@ -1702,13 +1702,13 @@
         <v>22.7957</v>
       </c>
       <c r="S16" t="n">
-        <v>6.681</v>
+        <v>7.616800000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>6.406900000000001</v>
+        <v>7.3429</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2741</v>
+        <v>0.2739999999999998</v>
       </c>
       <c r="V16" t="n">
         <v>4.4915</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. OULAI</t>
+          <t>J. YELAMOS MAÑAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4728</v>
+        <v>0.6027</v>
       </c>
       <c r="E17" t="n">
-        <v>6.2866</v>
+        <v>0.6027</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.8138</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3552</v>
+        <v>0.6027</v>
       </c>
       <c r="H17" t="n">
-        <v>2.7432</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.612</v>
+        <v>0.6027</v>
       </c>
       <c r="J17" t="n">
-        <v>8.136900000000001</v>
+        <v>0.6027</v>
       </c>
       <c r="K17" t="n">
-        <v>6.0879</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>2.0491</v>
+        <v>0.6027</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.7817</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-3.3446</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4371</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-4.3609</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.9467</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.204</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.8892</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6853</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2745</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0674</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. YELAMOS MAÑAS</t>
+          <t>K. OULAI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6027</v>
+        <v>0.2917</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6027</v>
+        <v>4.1473</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-3.8556</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6027</v>
+        <v>3.3552</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2.7432</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6027</v>
+        <v>0.612</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6027</v>
+        <v>8.136900000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>6.0879</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6027</v>
+        <v>2.0491</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-4.7817</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-3.3446</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-1.4371</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-4.3609</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-5.9467</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.0229</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-0.727</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.2745</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.0674</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. DAVID ROCHA</t>
+          <t>G. CARRAL ESCUDERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3737</v>
+        <v>-0.1169</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0179</v>
+        <v>3.7042</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.3916</v>
+        <v>-3.8211</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.2462</v>
+        <v>1.2939</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.5783</v>
+        <v>0.5728</v>
       </c>
       <c r="I19" t="n">
-        <v>2.3321</v>
+        <v>0.7211</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2628</v>
+        <v>4.9577</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.6333</v>
+        <v>3.5916</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8961</v>
+        <v>1.366</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.509</v>
+        <v>-3.6637</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.945</v>
+        <v>-3.0188</v>
       </c>
       <c r="O19" t="n">
-        <v>0.436</v>
+        <v>-0.6449</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9911</v>
+        <v>0.5947</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9822</v>
+        <v>1.5858</v>
       </c>
       <c r="S19" t="n">
-        <v>1.485</v>
+        <v>-0.7984</v>
       </c>
       <c r="T19" t="n">
-        <v>2.2725</v>
+        <v>-0.2623</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7875</v>
+        <v>-0.5361</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6036</v>
+        <v>-1.2071</v>
       </c>
       <c r="W19" t="n">
-        <v>1.4737</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.0772</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. CARRAL ESCUDERO</t>
+          <t>D. DAVID ROCHA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7751</v>
+        <v>-1.7273</v>
       </c>
       <c r="E20" t="n">
-        <v>3.093</v>
+        <v>1.388</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.8681</v>
+        <v>-3.1153</v>
       </c>
       <c r="G20" t="n">
-        <v>1.2939</v>
+        <v>-2.2462</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5728</v>
+        <v>-4.5783</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7211</v>
+        <v>2.3321</v>
       </c>
       <c r="J20" t="n">
-        <v>4.9577</v>
+        <v>0.2628</v>
       </c>
       <c r="K20" t="n">
-        <v>3.5916</v>
+        <v>-1.6333</v>
       </c>
       <c r="L20" t="n">
-        <v>1.366</v>
+        <v>1.8961</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.6637</v>
+        <v>-2.509</v>
       </c>
       <c r="N20" t="n">
-        <v>-3.0188</v>
+        <v>-2.945</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6449</v>
+        <v>0.436</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5947</v>
+        <v>0.9911</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5858</v>
+        <v>1.9822</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4566</v>
+        <v>0.1313</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8736</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5831</v>
+        <v>-0.5113</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2071</v>
+        <v>-0.6036</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.4737</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2071</v>
+        <v>-2.0772</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5126</v>
+        <v>-1.7447</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2486</v>
+        <v>-0.8411</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.264</v>
+        <v>-0.9036</v>
       </c>
       <c r="G21" t="n">
         <v>-2.6674</v>
@@ -2092,13 +2092,13 @@
         <v>0.9911</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9038</v>
+        <v>-0.1358</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3744</v>
+        <v>0.0331</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5294</v>
+        <v>-0.1689</v>
       </c>
       <c r="V21" t="n">
         <v>0.0674</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9549</v>
+        <v>-2.5932</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6392</v>
+        <v>-1.3335</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3158</v>
+        <v>-1.2596</v>
       </c>
       <c r="G22" t="n">
         <v>-0.3934</v>
@@ -2170,13 +2170,13 @@
         <v>0.7929</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3722</v>
+        <v>-1.0104</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1872</v>
+        <v>0.1184</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.185</v>
+        <v>-1.1288</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0702</v>
+        <v>-3.9507</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7169</v>
+        <v>-3.5132</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3533</v>
+        <v>-0.4375</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4202</v>
@@ -2248,13 +2248,13 @@
         <v>0.5947</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0048</v>
+        <v>0.1147</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1248</v>
+        <v>0.0789</v>
       </c>
       <c r="U23" t="n">
-        <v>0.12</v>
+        <v>0.0358</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2666</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.12</v>
+        <v>-4.3671</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.42</v>
+        <v>-2.9107</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7</v>
+        <v>-1.4564</v>
       </c>
       <c r="G24" t="n">
         <v>-2.0939</v>
@@ -2326,13 +2326,13 @@
         <v>0.9911</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8447</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8736</v>
+        <v>-0.3642</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0289</v>
+        <v>0.2724</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1992</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.7213</v>
+        <v>-6.7719</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.312</v>
+        <v>-2.8027</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.4093</v>
+        <v>-3.9692</v>
       </c>
       <c r="G25" t="n">
         <v>-5.5721</v>
@@ -2404,13 +2404,13 @@
         <v>0.9911</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.7341</v>
+        <v>-0.7846</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9984</v>
+        <v>-0.489</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.7357</v>
+        <v>-0.2956</v>
       </c>
       <c r="V25" t="n">
         <v>-1.4063</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C. RAMON PEREZ</t>
+          <t>A. MORENO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.3225</v>
+        <v>-7.3257</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.6132</v>
+        <v>-4.1897</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.7093</v>
+        <v>-3.136</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.726</v>
+        <v>-3.2482</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.6565</v>
+        <v>-2.6629</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.0695</v>
+        <v>-0.5853</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3958</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.4243</v>
+        <v>0.1424</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.0285</v>
+        <v>-0.2177</v>
       </c>
       <c r="M26" t="n">
-        <v>-4.1218</v>
+        <v>-3.1728</v>
       </c>
       <c r="N26" t="n">
-        <v>-3.0808</v>
+        <v>-2.8053</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.041</v>
+        <v>-0.3676</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.3876</v>
+        <v>-2.1805</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.9733</v>
+        <v>-3.9645</v>
       </c>
       <c r="R26" t="n">
-        <v>1.5858</v>
+        <v>1.784</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.3953</v>
+        <v>-1.5601</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5688</v>
+        <v>-0.4164</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8264</v>
+        <v>-1.1437</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.8137</v>
+        <v>-0.337</v>
       </c>
       <c r="W26" t="n">
-        <v>0.5331</v>
+        <v>0.2666</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.3468</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A. MORENO</t>
+          <t>C. RAMON PEREZ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-8.424099999999999</v>
+        <v>-7.4586</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.2084</v>
+        <v>-2.4095</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.2157</v>
+        <v>-5.0491</v>
       </c>
       <c r="G27" t="n">
-        <v>-3.2482</v>
+        <v>-3.726</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.6629</v>
+        <v>-2.6565</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5853</v>
+        <v>-1.0695</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.3958</v>
       </c>
       <c r="K27" t="n">
-        <v>0.1424</v>
+        <v>0.4243</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.2177</v>
+        <v>-0.0285</v>
       </c>
       <c r="M27" t="n">
-        <v>-3.1728</v>
+        <v>-4.1218</v>
       </c>
       <c r="N27" t="n">
-        <v>-2.8053</v>
+        <v>-3.0808</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.3676</v>
+        <v>-1.041</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.1805</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q27" t="n">
-        <v>-3.9645</v>
+        <v>-2.9733</v>
       </c>
       <c r="R27" t="n">
-        <v>1.784</v>
+        <v>1.5858</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.6585</v>
+        <v>-0.5313</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.4351</v>
+        <v>-0.3651</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.2233</v>
+        <v>-0.1662</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.337</v>
+        <v>-1.8137</v>
       </c>
       <c r="W27" t="n">
-        <v>0.2666</v>
+        <v>0.5331</v>
       </c>
       <c r="X27" t="n">
-        <v>-0.6036</v>
+        <v>-2.3468</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-37.19889999999999</v>
+        <v>-35.1617</v>
       </c>
       <c r="E28" t="n">
-        <v>-8.158099999999999</v>
+        <v>-8.158199999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>-29.0409</v>
+        <v>-27.0034</v>
       </c>
       <c r="G28" t="n">
         <v>-16.1156</v>
@@ -2626,10 +2626,10 @@
         <v>-21.748</v>
       </c>
       <c r="O28" t="n">
-        <v>-5.798600000000001</v>
+        <v>-5.7986</v>
       </c>
       <c r="P28" t="n">
-        <v>-9.911199999999999</v>
+        <v>-9.911200000000001</v>
       </c>
       <c r="Q28" t="n">
         <v>-22.7955</v>
@@ -2638,16 +2638,16 @@
         <v>12.8845</v>
       </c>
       <c r="S28" t="n">
-        <v>-6.681</v>
+        <v>-4.6435</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.2742</v>
+        <v>-0.2739999999999999</v>
       </c>
       <c r="U28" t="n">
-        <v>-6.4068</v>
+        <v>-4.3694</v>
       </c>
       <c r="V28" t="n">
-        <v>-4.4916</v>
+        <v>-4.491600000000001</v>
       </c>
       <c r="W28" t="n">
         <v>3.4805</v>
